--- a/Output/Models/Exposure_models_malf_div10_Masculino.xlsx
+++ b/Output/Models/Exposure_models_malf_div10_Masculino.xlsx
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.9215645879533392</v>
+        <v>0.9147553864659314</v>
       </c>
       <c r="C3">
-        <v>0.03890283983790031</v>
+        <v>0.0396935831900759</v>
       </c>
       <c r="D3">
-        <v>-2.099651713060054</v>
+        <v>-2.24465970271874</v>
       </c>
       <c r="E3">
-        <v>0.03575949015614084</v>
+        <v>0.02478998686477853</v>
       </c>
       <c r="F3">
-        <v>0.8539090588865009</v>
+        <v>0.8462871297307211</v>
       </c>
       <c r="G3">
-        <v>0.9945804894927246</v>
+        <v>0.9887630186869184</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -564,22 +564,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.9076214707134653</v>
+        <v>0.9238760272006321</v>
       </c>
       <c r="C4">
-        <v>0.03899064352370902</v>
+        <v>0.03986808746082967</v>
       </c>
       <c r="D4">
-        <v>-2.485926391948835</v>
+        <v>-1.985984055946728</v>
       </c>
       <c r="E4">
-        <v>0.01292146890565319</v>
+        <v>0.04703509432426437</v>
       </c>
       <c r="F4">
-        <v>0.8408448432494287</v>
+        <v>0.8544328174355047</v>
       </c>
       <c r="G4">
-        <v>0.9797012382410583</v>
+        <v>0.9989631674001701</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.036929827106282</v>
+        <v>1.066006336278343</v>
       </c>
       <c r="C5">
-        <v>0.03773564583885494</v>
+        <v>0.0382184262295036</v>
       </c>
       <c r="D5">
-        <v>0.9610080075718155</v>
+        <v>1.672472574304346</v>
       </c>
       <c r="E5">
-        <v>0.3365481416008784</v>
+        <v>0.09443117156458601</v>
       </c>
       <c r="F5">
-        <v>0.9630054103692735</v>
+        <v>0.9890726725164395</v>
       </c>
       <c r="G5">
-        <v>1.116528998451171</v>
+        <v>1.148924179751501</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="O5">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="6">
@@ -879,22 +879,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.6274296128596341</v>
+        <v>0.6003919459049309</v>
       </c>
       <c r="C9">
-        <v>0.2412033934671904</v>
+        <v>0.2463359434171505</v>
       </c>
       <c r="D9">
-        <v>-1.932492649913027</v>
+        <v>-2.071044066020111</v>
       </c>
       <c r="E9">
-        <v>0.05329872838455793</v>
+        <v>0.03835467820483612</v>
       </c>
       <c r="F9">
-        <v>0.391068028125788</v>
+        <v>0.3704702364071443</v>
       </c>
       <c r="G9">
-        <v>1.006648180828953</v>
+        <v>0.973007959298935</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -942,22 +942,22 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.540514069712716</v>
+        <v>0.6013639443457214</v>
       </c>
       <c r="C10">
-        <v>0.2434232105630467</v>
+        <v>0.2496169803000816</v>
       </c>
       <c r="D10">
-        <v>-2.527427889467766</v>
+        <v>-2.037341219658585</v>
       </c>
       <c r="E10">
-        <v>0.01149014171543231</v>
+        <v>0.04161585987417881</v>
       </c>
       <c r="F10">
-        <v>0.3354322309957004</v>
+        <v>0.3686914165176872</v>
       </c>
       <c r="G10">
-        <v>0.8709820719677585</v>
+        <v>0.9808706613642983</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1005,22 +1005,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.207368710247338</v>
+        <v>1.445724615121156</v>
       </c>
       <c r="C11">
-        <v>0.2364515358212697</v>
+        <v>0.2392191084551177</v>
       </c>
       <c r="D11">
-        <v>0.7969640434140357</v>
+        <v>1.540891369446309</v>
       </c>
       <c r="E11">
-        <v>0.4254719142223145</v>
+        <v>0.123343226686984</v>
       </c>
       <c r="F11">
-        <v>0.759577347398237</v>
+        <v>0.9046110765128137</v>
       </c>
       <c r="G11">
-        <v>1.919145176560993</v>
+        <v>2.310517433441584</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="O11">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="12">
@@ -1257,22 +1257,22 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.6171727778266285</v>
+        <v>0.5906406319849749</v>
       </c>
       <c r="C15">
-        <v>0.2272593646081519</v>
+        <v>0.2322332811524928</v>
       </c>
       <c r="D15">
-        <v>-2.123592425848846</v>
+        <v>-2.267321512310516</v>
       </c>
       <c r="E15">
-        <v>0.03370423944730076</v>
+        <v>0.02337059225228851</v>
       </c>
       <c r="F15">
-        <v>0.3953331565901376</v>
+        <v>0.3746674744094021</v>
       </c>
       <c r="G15">
-        <v>0.9634968161426899</v>
+        <v>0.931109263491638</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1320,22 +1320,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.5623963035608439</v>
+        <v>0.6255890735551961</v>
       </c>
       <c r="C16">
-        <v>0.228659057168851</v>
+        <v>0.2337241559245862</v>
       </c>
       <c r="D16">
-        <v>-2.51705975809271</v>
+        <v>-2.006902340037422</v>
       </c>
       <c r="E16">
-        <v>0.01183387561116771</v>
+        <v>0.04476006265006829</v>
       </c>
       <c r="F16">
-        <v>0.3592588829648501</v>
+        <v>0.3956788097296762</v>
       </c>
       <c r="G16">
-        <v>0.8803946603871359</v>
+        <v>0.9890893303561618</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1383,22 +1383,22 @@
         </is>
       </c>
       <c r="B17">
-        <v>1.226053638486023</v>
+        <v>1.430926441310913</v>
       </c>
       <c r="C17">
-        <v>0.2197789051695183</v>
+        <v>0.2223072868176574</v>
       </c>
       <c r="D17">
-        <v>0.9272982191081858</v>
+        <v>1.611832435573408</v>
       </c>
       <c r="E17">
-        <v>0.3537717187356902</v>
+        <v>0.1069984078882004</v>
       </c>
       <c r="F17">
-        <v>0.7969541330606931</v>
+        <v>0.9255268092192366</v>
       </c>
       <c r="G17">
-        <v>1.886190763164455</v>
+        <v>2.212308125542038</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="O17">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="18">
@@ -1635,22 +1635,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.9491668810353985</v>
+        <v>0.9450373643366001</v>
       </c>
       <c r="C21">
-        <v>0.02298084946222715</v>
+        <v>0.0234473001622707</v>
       </c>
       <c r="D21">
-        <v>-2.270179201394447</v>
+        <v>-2.410973242048324</v>
       </c>
       <c r="E21">
-        <v>0.02319671240423872</v>
+        <v>0.01591001564633431</v>
       </c>
       <c r="F21">
-        <v>0.907363367180003</v>
+        <v>0.9025901747533168</v>
       </c>
       <c r="G21">
-        <v>0.9928963419081279</v>
+        <v>0.9894807687623633</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1698,22 +1698,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.9396050617204713</v>
+        <v>0.9489562936581288</v>
       </c>
       <c r="C22">
-        <v>0.02304723952083809</v>
+        <v>0.0232899562075846</v>
       </c>
       <c r="D22">
-        <v>-2.702954471149122</v>
+        <v>-2.249576432027915</v>
       </c>
       <c r="E22">
-        <v>0.006872615941757103</v>
+        <v>0.02447584592569372</v>
       </c>
       <c r="F22">
-        <v>0.8981058015568811</v>
+        <v>0.9066126276836872</v>
       </c>
       <c r="G22">
-        <v>0.9830219006271672</v>
+        <v>0.9932776356470068</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1761,22 +1761,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.006326164887336</v>
+        <v>1.019444025451837</v>
       </c>
       <c r="C23">
-        <v>0.02118521284906921</v>
+        <v>0.02126817821381145</v>
       </c>
       <c r="D23">
-        <v>0.2976717177488099</v>
+        <v>0.9054562835523657</v>
       </c>
       <c r="E23">
-        <v>0.7659537313636179</v>
+        <v>0.3652237097159557</v>
       </c>
       <c r="F23">
-        <v>0.9653968530583216</v>
+        <v>0.9778221680774575</v>
       </c>
       <c r="G23">
-        <v>1.048990730525692</v>
+        <v>1.06283755365538</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="O23">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="24">
@@ -2013,22 +2013,22 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.6581864964972078</v>
+        <v>0.6318011281682795</v>
       </c>
       <c r="C27">
-        <v>0.2269512464553001</v>
+        <v>0.2317341426241931</v>
       </c>
       <c r="D27">
-        <v>-1.842981543485998</v>
+        <v>-1.981497416714027</v>
       </c>
       <c r="E27">
-        <v>0.06533170526920824</v>
+        <v>0.04753551878248338</v>
       </c>
       <c r="F27">
-        <v>0.4218593865130259</v>
+        <v>0.401169527765906</v>
       </c>
       <c r="G27">
-        <v>1.026904883525432</v>
+        <v>0.9950223980811413</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2076,22 +2076,22 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.5715162219844928</v>
+        <v>0.6336047252163257</v>
       </c>
       <c r="C28">
-        <v>0.2290953897142964</v>
+        <v>0.2342749899176021</v>
       </c>
       <c r="D28">
-        <v>-2.442050064486552</v>
+        <v>-1.94783907980293</v>
       </c>
       <c r="E28">
-        <v>0.0146041212034774</v>
+        <v>0.05143422106309757</v>
       </c>
       <c r="F28">
-        <v>0.3647726033421912</v>
+        <v>0.4003162082688482</v>
       </c>
       <c r="G28">
-        <v>0.8954367433264101</v>
+        <v>1.002844600153793</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2139,22 +2139,22 @@
         </is>
       </c>
       <c r="B29">
-        <v>1.157014838216565</v>
+        <v>1.344293408820236</v>
       </c>
       <c r="C29">
-        <v>0.2209927452344256</v>
+        <v>0.2236485633781956</v>
       </c>
       <c r="D29">
-        <v>0.6599459756383094</v>
+        <v>1.322917187304041</v>
       </c>
       <c r="E29">
-        <v>0.5092884988851185</v>
+        <v>0.1858629189553842</v>
       </c>
       <c r="F29">
-        <v>0.7502906991805834</v>
+        <v>0.8672095802630143</v>
       </c>
       <c r="G29">
-        <v>1.784219552921717</v>
+        <v>2.083838566969532</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="O29">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="30">
@@ -2391,22 +2391,22 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.6991982328723522</v>
+        <v>0.6777787060090538</v>
       </c>
       <c r="C33">
-        <v>0.1581770773126285</v>
+        <v>0.1616783344642616</v>
       </c>
       <c r="D33">
-        <v>-2.262154466878073</v>
+        <v>-2.405606403140611</v>
       </c>
       <c r="E33">
-        <v>0.0236878614066209</v>
+        <v>0.01614564942851254</v>
       </c>
       <c r="F33">
-        <v>0.5128138543317481</v>
+        <v>0.4937044850136378</v>
       </c>
       <c r="G33">
-        <v>0.95332480728096</v>
+        <v>0.9304836967535702</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2454,22 +2454,22 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.6506642273722765</v>
+        <v>0.7021982116973265</v>
       </c>
       <c r="C34">
-        <v>0.1593277942501362</v>
+        <v>0.1612660315459873</v>
       </c>
       <c r="D34">
-        <v>-2.6973419899675</v>
+        <v>-2.192275450545687</v>
       </c>
       <c r="E34">
-        <v>0.006989544700487133</v>
+        <v>0.02835962327956257</v>
       </c>
       <c r="F34">
-        <v>0.4761424103608166</v>
+        <v>0.5119055335632368</v>
       </c>
       <c r="G34">
-        <v>0.8891540168857044</v>
+        <v>0.9632291432341235</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2517,22 +2517,22 @@
         </is>
       </c>
       <c r="B35">
-        <v>1.091620526217161</v>
+        <v>1.192437893709174</v>
       </c>
       <c r="C35">
-        <v>0.1462916188730368</v>
+        <v>0.147174037352383</v>
       </c>
       <c r="D35">
-        <v>0.599236744665018</v>
+        <v>1.19586215641883</v>
       </c>
       <c r="E35">
-        <v>0.5490150228540687</v>
+        <v>0.2317503552606103</v>
       </c>
       <c r="F35">
-        <v>0.8194982708832897</v>
+        <v>0.8936367100513127</v>
       </c>
       <c r="G35">
-        <v>1.454103584592358</v>
+        <v>1.591147850530811</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="O35">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="36">
@@ -2769,22 +2769,22 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.8555442720418867</v>
+        <v>0.8555978217412633</v>
       </c>
       <c r="C39">
-        <v>0.08806479462265654</v>
+        <v>0.08892245959811547</v>
       </c>
       <c r="D39">
-        <v>-1.771620972427521</v>
+        <v>-1.753829666502881</v>
       </c>
       <c r="E39">
-        <v>0.07645749593468344</v>
+        <v>0.07945969808317413</v>
       </c>
       <c r="F39">
-        <v>0.7199156239105399</v>
+        <v>0.718751452580824</v>
       </c>
       <c r="G39">
-        <v>1.01672470649788</v>
+        <v>1.018498995640048</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2832,22 +2832,22 @@
         </is>
       </c>
       <c r="B40">
-        <v>1.016472845434968</v>
+        <v>1.06599561351073</v>
       </c>
       <c r="C40">
-        <v>0.09241396012795872</v>
+        <v>0.09355355802817965</v>
       </c>
       <c r="D40">
-        <v>0.1767983962518661</v>
+        <v>0.6831296657945359</v>
       </c>
       <c r="E40">
-        <v>0.8596667488162106</v>
+        <v>0.4945249113111796</v>
       </c>
       <c r="F40">
-        <v>0.848072294753009</v>
+        <v>0.8874062530916312</v>
       </c>
       <c r="G40">
-        <v>1.218312462155803</v>
+        <v>1.28052585167752</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2895,22 +2895,22 @@
         </is>
       </c>
       <c r="B41">
-        <v>1.091425488245821</v>
+        <v>1.066440846197095</v>
       </c>
       <c r="C41">
-        <v>0.08569966765807213</v>
+        <v>0.08518322856952956</v>
       </c>
       <c r="D41">
-        <v>1.020828103587445</v>
+        <v>0.7551579473395617</v>
       </c>
       <c r="E41">
-        <v>0.3073358869701511</v>
+        <v>0.4501542174037502</v>
       </c>
       <c r="F41">
-        <v>0.9226700049077188</v>
+        <v>0.9024614827774373</v>
       </c>
       <c r="G41">
-        <v>1.291046192090928</v>
+        <v>1.260215643705264</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="O41">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="42">
@@ -3147,22 +3147,22 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.4237599766427979</v>
+        <v>0.4359502037554751</v>
       </c>
       <c r="C45">
-        <v>0.5596305663955203</v>
+        <v>0.5611174581820809</v>
       </c>
       <c r="D45">
-        <v>-1.534205113910805</v>
+        <v>-1.479596190814554</v>
       </c>
       <c r="E45">
-        <v>0.1249791999534431</v>
+        <v>0.1389810436750945</v>
       </c>
       <c r="F45">
-        <v>0.141501659840261</v>
+        <v>0.1451485957752105</v>
       </c>
       <c r="G45">
-        <v>1.269048843716895</v>
+        <v>1.309365613490136</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3210,22 +3210,22 @@
         </is>
       </c>
       <c r="B46">
-        <v>1.054900252303561</v>
+        <v>1.389737284694388</v>
       </c>
       <c r="C46">
-        <v>0.578758149106199</v>
+        <v>0.5717933977337983</v>
       </c>
       <c r="D46">
-        <v>0.09234637121067241</v>
+        <v>0.5755832906894846</v>
       </c>
       <c r="E46">
-        <v>0.9264228468439309</v>
+        <v>0.5648968778858985</v>
       </c>
       <c r="F46">
-        <v>0.3392903959316055</v>
+        <v>0.4531284041955986</v>
       </c>
       <c r="G46">
-        <v>3.279829183654345</v>
+        <v>4.262301154787087</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3273,22 +3273,22 @@
         </is>
       </c>
       <c r="B47">
-        <v>1.47810346326845</v>
+        <v>1.350902153693446</v>
       </c>
       <c r="C47">
-        <v>0.5362395151934493</v>
+        <v>0.5305606552465035</v>
       </c>
       <c r="D47">
-        <v>0.7287038929729055</v>
+        <v>0.5668958455242424</v>
       </c>
       <c r="E47">
-        <v>0.4661828109633587</v>
+        <v>0.5707849469189419</v>
       </c>
       <c r="F47">
-        <v>0.516721975258422</v>
+        <v>0.4775400994701923</v>
       </c>
       <c r="G47">
-        <v>4.228172891299103</v>
+        <v>3.821535889610674</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="O47">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="48">
@@ -3525,22 +3525,22 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.4099645082741113</v>
+        <v>0.4124109239039981</v>
       </c>
       <c r="C51">
-        <v>0.5058320428498728</v>
+        <v>0.5116168909800767</v>
       </c>
       <c r="D51">
-        <v>-1.762807834774724</v>
+        <v>-1.731246669515548</v>
       </c>
       <c r="E51">
-        <v>0.07793290556585386</v>
+        <v>0.08340777878750036</v>
       </c>
       <c r="F51">
-        <v>0.1521182234760632</v>
+        <v>0.15130074733418</v>
       </c>
       <c r="G51">
-        <v>1.104870239763752</v>
+        <v>1.124137012883917</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3588,22 +3588,22 @@
         </is>
       </c>
       <c r="B52">
-        <v>1.07621235085866</v>
+        <v>1.416175817934785</v>
       </c>
       <c r="C52">
-        <v>0.5285456720155967</v>
+        <v>0.5309725013720765</v>
       </c>
       <c r="D52">
-        <v>0.1389620580701446</v>
+        <v>0.6553261268195437</v>
       </c>
       <c r="E52">
-        <v>0.8894801313601483</v>
+        <v>0.5122578027490079</v>
       </c>
       <c r="F52">
-        <v>0.3819434618461859</v>
+        <v>0.5002102211112219</v>
       </c>
       <c r="G52">
-        <v>3.032472446424962</v>
+        <v>4.009422164241062</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="B53">
-        <v>1.586529056586919</v>
+        <v>1.391370490042604</v>
       </c>
       <c r="C53">
-        <v>0.4832101517274869</v>
+        <v>0.4842426620265166</v>
       </c>
       <c r="D53">
-        <v>0.9551716683147775</v>
+        <v>0.6820737852309176</v>
       </c>
       <c r="E53">
-        <v>0.3394908907313913</v>
+        <v>0.4951922958634699</v>
       </c>
       <c r="F53">
-        <v>0.6153735189947349</v>
+        <v>0.538585537014128</v>
       </c>
       <c r="G53">
-        <v>4.090319732162729</v>
+        <v>3.59443710890182</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="O53">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="54">
@@ -3903,22 +3903,22 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.9245457780889069</v>
+        <v>0.9233903048545612</v>
       </c>
       <c r="C57">
-        <v>0.04203149831719654</v>
+        <v>0.04239608148404206</v>
       </c>
       <c r="D57">
-        <v>-1.866521916426548</v>
+        <v>-1.879967807727787</v>
       </c>
       <c r="E57">
-        <v>0.06196838069834365</v>
+        <v>0.06011246544762619</v>
       </c>
       <c r="F57">
-        <v>0.8514343034955768</v>
+        <v>0.8497627711992551</v>
       </c>
       <c r="G57">
-        <v>1.003935232903689</v>
+        <v>1.003397282156843</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3966,22 +3966,22 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.9654514786717611</v>
+        <v>0.9796962779215472</v>
       </c>
       <c r="C58">
-        <v>0.04223051905042291</v>
+        <v>0.04170511975694716</v>
       </c>
       <c r="D58">
-        <v>-0.8325598239664328</v>
+        <v>-0.491850304244699</v>
       </c>
       <c r="E58">
-        <v>0.4050930254270174</v>
+        <v>0.622825171887488</v>
       </c>
       <c r="F58">
-        <v>0.8887585035747239</v>
+        <v>0.9028009258247583</v>
       </c>
       <c r="G58">
-        <v>1.048762463504376</v>
+        <v>1.063141130583688</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4029,22 +4029,22 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.9860779662603749</v>
+        <v>0.9775451853149215</v>
       </c>
       <c r="C59">
-        <v>0.03718786916240968</v>
+        <v>0.03783373933283734</v>
       </c>
       <c r="D59">
-        <v>-0.3770007406989703</v>
+        <v>-0.6002780376814616</v>
       </c>
       <c r="E59">
-        <v>0.7061730544621516</v>
+        <v>0.5483209529656341</v>
       </c>
       <c r="F59">
-        <v>0.9167625903563218</v>
+        <v>0.9076798693904622</v>
       </c>
       <c r="G59">
-        <v>1.060634198834695</v>
+        <v>1.052788126692838</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="O59">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="60">
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.5516222417461728</v>
+        <v>0.5595925708447244</v>
       </c>
       <c r="C63">
-        <v>0.4885941787681164</v>
+        <v>0.4897476519221335</v>
       </c>
       <c r="D63">
-        <v>-1.217558123877689</v>
+        <v>-1.18539886782894</v>
       </c>
       <c r="E63">
-        <v>0.2233919360119208</v>
+        <v>0.2358597791675618</v>
       </c>
       <c r="F63">
-        <v>0.2117140352779265</v>
+        <v>0.2142880649178205</v>
       </c>
       <c r="G63">
-        <v>1.437255197510273</v>
+        <v>1.461321914800521</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4344,22 +4344,22 @@
         </is>
       </c>
       <c r="B64">
-        <v>1.06792726073829</v>
+        <v>1.332479929090431</v>
       </c>
       <c r="C64">
-        <v>0.4981773221944989</v>
+        <v>0.4887568574729155</v>
       </c>
       <c r="D64">
-        <v>0.1319201564738129</v>
+        <v>0.5872895898223335</v>
       </c>
       <c r="E64">
-        <v>0.8950474454030166</v>
+        <v>0.5570092315142178</v>
       </c>
       <c r="F64">
-        <v>0.4022465865167292</v>
+        <v>0.5112461902453284</v>
       </c>
       <c r="G64">
-        <v>2.835247513481523</v>
+        <v>3.472891916469523</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4407,22 +4407,22 @@
         </is>
       </c>
       <c r="B65">
-        <v>1.202538459971979</v>
+        <v>1.063306963276457</v>
       </c>
       <c r="C65">
-        <v>0.4541015854020505</v>
+        <v>0.4567318745702157</v>
       </c>
       <c r="D65">
-        <v>0.4061529661203678</v>
+        <v>0.1343979516480329</v>
       </c>
       <c r="E65">
-        <v>0.6846302102912245</v>
+        <v>0.8930879012889352</v>
       </c>
       <c r="F65">
-        <v>0.4938181006653043</v>
+        <v>0.4343979644098128</v>
       </c>
       <c r="G65">
-        <v>2.928403689057772</v>
+        <v>2.602732495968991</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="O65">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="66">
@@ -4659,22 +4659,22 @@
         </is>
       </c>
       <c r="B69">
-        <v>0.5616421396997502</v>
+        <v>0.5581575723427373</v>
       </c>
       <c r="C69">
-        <v>0.3053088940939092</v>
+        <v>0.3083323849522541</v>
       </c>
       <c r="D69">
-        <v>-1.889530259901892</v>
+        <v>-1.891186256169714</v>
       </c>
       <c r="E69">
-        <v>0.05882081203999534</v>
+        <v>0.05859948534878703</v>
       </c>
       <c r="F69">
-        <v>0.3087310311212035</v>
+        <v>0.3050027949862132</v>
       </c>
       <c r="G69">
-        <v>1.021736920778384</v>
+        <v>1.02143285466489</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4722,22 +4722,22 @@
         </is>
       </c>
       <c r="B70">
-        <v>0.7877851710674993</v>
+        <v>0.9045513476168043</v>
       </c>
       <c r="C70">
-        <v>0.3081355851965326</v>
+        <v>0.3033349552392349</v>
       </c>
       <c r="D70">
-        <v>-0.7741068000636147</v>
+        <v>-0.330711001034229</v>
       </c>
       <c r="E70">
-        <v>0.4388676365212326</v>
+        <v>0.7408627918411497</v>
       </c>
       <c r="F70">
-        <v>0.4306478823115485</v>
+        <v>0.4991534106950636</v>
       </c>
       <c r="G70">
-        <v>1.44109724265375</v>
+        <v>1.639201742278045</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4785,22 +4785,22 @@
         </is>
       </c>
       <c r="B71">
-        <v>1.0215238101029</v>
+        <v>0.9498768022533964</v>
       </c>
       <c r="C71">
-        <v>0.266138081300388</v>
+        <v>0.2721732369756755</v>
       </c>
       <c r="D71">
-        <v>0.08001652322768806</v>
+        <v>-0.1889347579023468</v>
       </c>
       <c r="E71">
-        <v>0.9362241144726268</v>
+        <v>0.8501439512811031</v>
       </c>
       <c r="F71">
-        <v>0.6063331992323731</v>
+        <v>0.5571767710463185</v>
       </c>
       <c r="G71">
-        <v>1.721018898401484</v>
+        <v>1.619353114389135</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="O71">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="72">
@@ -4974,22 +4974,22 @@
         </is>
       </c>
       <c r="B74">
-        <v>0.9779011302352247</v>
+        <v>1.017910991664521</v>
       </c>
       <c r="C74">
-        <v>0.07387191785372475</v>
+        <v>0.07729353618846925</v>
       </c>
       <c r="D74">
-        <v>-0.3025061286605286</v>
+        <v>0.2296761238637288</v>
       </c>
       <c r="E74">
-        <v>0.7622662621842868</v>
+        <v>0.8183434493595565</v>
       </c>
       <c r="F74">
-        <v>0.8460870689010721</v>
+        <v>0.8748174286424384</v>
       </c>
       <c r="G74">
-        <v>1.130250840208909</v>
+        <v>1.184410315829395</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="O74">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="75">
@@ -5037,22 +5037,22 @@
         </is>
       </c>
       <c r="B75">
-        <v>0.9101313217458751</v>
+        <v>0.871169898549994</v>
       </c>
       <c r="C75">
-        <v>0.07707203453524722</v>
+        <v>0.07870509207550223</v>
       </c>
       <c r="D75">
-        <v>-1.221796996016173</v>
+        <v>-1.752342269522996</v>
       </c>
       <c r="E75">
-        <v>0.2217844048438813</v>
+        <v>0.07971497183621327</v>
       </c>
       <c r="F75">
-        <v>0.7825286121594365</v>
+        <v>0.7466360668498272</v>
       </c>
       <c r="G75">
-        <v>1.058541515225929</v>
+        <v>1.016475128695134</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="O75">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="76">
@@ -5100,22 +5100,22 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.9067043249824186</v>
+        <v>0.9346054448404151</v>
       </c>
       <c r="C76">
-        <v>0.07691713244809201</v>
+        <v>0.079048716824158</v>
       </c>
       <c r="D76">
-        <v>-1.273303764694679</v>
+        <v>-0.8555587693111992</v>
       </c>
       <c r="E76">
-        <v>0.202910271336309</v>
+        <v>0.3922418841645382</v>
       </c>
       <c r="F76">
-        <v>0.7798188080090407</v>
+        <v>0.800464206974434</v>
       </c>
       <c r="G76">
-        <v>1.054235579468471</v>
+        <v>1.091225978519297</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="O76">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="77">
@@ -5163,22 +5163,22 @@
         </is>
       </c>
       <c r="B77">
-        <v>0.9665554055869778</v>
+        <v>0.9531361950296817</v>
       </c>
       <c r="C77">
-        <v>0.07224215972739759</v>
+        <v>0.07439233101355917</v>
       </c>
       <c r="D77">
-        <v>-0.470869864590569</v>
+        <v>-0.6451938391563432</v>
       </c>
       <c r="E77">
-        <v>0.6377336693444678</v>
+        <v>0.5188015781609303</v>
       </c>
       <c r="F77">
-        <v>0.8389462095039117</v>
+        <v>0.8238195521506081</v>
       </c>
       <c r="G77">
-        <v>1.113574793575667</v>
+        <v>1.102751936275453</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="O77">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="78">
@@ -5226,22 +5226,22 @@
         </is>
       </c>
       <c r="B78">
-        <v>0.628906096937383</v>
+        <v>0.8703927382431438</v>
       </c>
       <c r="C78">
-        <v>0.5436369414937298</v>
+        <v>0.5461934346132492</v>
       </c>
       <c r="D78">
-        <v>-0.8530938342782695</v>
+        <v>-0.2541420989885124</v>
       </c>
       <c r="E78">
-        <v>0.3936072703595073</v>
+        <v>0.7993857804980095</v>
       </c>
       <c r="F78">
-        <v>0.2166911634949115</v>
+        <v>0.2983970769750418</v>
       </c>
       <c r="G78">
-        <v>1.825283838924521</v>
+        <v>2.538843632338138</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="O78">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="79">
@@ -5289,22 +5289,22 @@
         </is>
       </c>
       <c r="B79">
-        <v>0.4145443557307436</v>
+        <v>0.3138360762250854</v>
       </c>
       <c r="C79">
-        <v>0.5140342286671711</v>
+        <v>0.5460602210320107</v>
       </c>
       <c r="D79">
-        <v>-1.713067439513389</v>
+        <v>-2.122264971870567</v>
       </c>
       <c r="E79">
-        <v>0.08670013337847249</v>
+        <v>0.03381549322298054</v>
       </c>
       <c r="F79">
-        <v>0.1513645860875156</v>
+        <v>0.1076206380464336</v>
       </c>
       <c r="G79">
-        <v>1.135318553105012</v>
+        <v>0.9151876863790949</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         </is>
       </c>
       <c r="O79">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="80">
@@ -5352,22 +5352,22 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.422537537548439</v>
+        <v>0.4790350051826305</v>
       </c>
       <c r="C80">
-        <v>0.5220165761823304</v>
+        <v>0.5731115012047083</v>
       </c>
       <c r="D80">
-        <v>-1.650286655958818</v>
+        <v>-1.284185717754972</v>
       </c>
       <c r="E80">
-        <v>0.09888432023131045</v>
+        <v>0.1990769812711287</v>
       </c>
       <c r="F80">
-        <v>0.1518881812525253</v>
+        <v>0.1557879477050247</v>
       </c>
       <c r="G80">
-        <v>1.17545663635715</v>
+        <v>1.472992869928675</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="O80">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="81">
@@ -5415,22 +5415,22 @@
         </is>
       </c>
       <c r="B81">
-        <v>0.5328766075426816</v>
+        <v>0.5290043433306257</v>
       </c>
       <c r="C81">
-        <v>0.5262268030620965</v>
+        <v>0.520390906114967</v>
       </c>
       <c r="D81">
-        <v>-1.196186479866552</v>
+        <v>-1.223615995630021</v>
       </c>
       <c r="E81">
-        <v>0.2316237957195551</v>
+        <v>0.2210971225648322</v>
       </c>
       <c r="F81">
-        <v>0.1899772465737879</v>
+        <v>0.1907663171185499</v>
       </c>
       <c r="G81">
-        <v>1.494692043322709</v>
+        <v>1.466954960863239</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="O81">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="82">
@@ -5478,22 +5478,22 @@
         </is>
       </c>
       <c r="B82">
-        <v>0.6996123129980387</v>
+        <v>0.8890883111039378</v>
       </c>
       <c r="C82">
-        <v>0.4465170910038513</v>
+        <v>0.4507184902358971</v>
       </c>
       <c r="D82">
-        <v>-0.8000341826447935</v>
+        <v>-0.2608251344772243</v>
       </c>
       <c r="E82">
-        <v>0.4236909925906922</v>
+        <v>0.7942273606471306</v>
       </c>
       <c r="F82">
-        <v>0.2915958960680614</v>
+        <v>0.3675298574543157</v>
       </c>
       <c r="G82">
-        <v>1.678546903774742</v>
+        <v>2.150785871974795</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="O82">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="83">
@@ -5541,22 +5541,22 @@
         </is>
       </c>
       <c r="B83">
-        <v>0.4768693607482274</v>
+        <v>0.3655410807506998</v>
       </c>
       <c r="C83">
-        <v>0.4384516437467241</v>
+        <v>0.4610426632266808</v>
       </c>
       <c r="D83">
-        <v>-1.688926733436466</v>
+        <v>-2.182827513250576</v>
       </c>
       <c r="E83">
-        <v>0.0912334714143766</v>
+        <v>0.02904851472464896</v>
       </c>
       <c r="F83">
-        <v>0.2019243547506643</v>
+        <v>0.1480798497555395</v>
       </c>
       <c r="G83">
-        <v>1.126186028927622</v>
+        <v>0.902352899040479</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="O83">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="84">
@@ -5604,22 +5604,22 @@
         </is>
       </c>
       <c r="B84">
-        <v>0.4726057622546865</v>
+        <v>0.5225471270906458</v>
       </c>
       <c r="C84">
-        <v>0.4409862101016945</v>
+        <v>0.4746154834294857</v>
       </c>
       <c r="D84">
-        <v>-1.699585393981517</v>
+        <v>-1.367507227391505</v>
       </c>
       <c r="E84">
-        <v>0.08920893963200148</v>
+        <v>0.1714663734459378</v>
       </c>
       <c r="F84">
-        <v>0.1991273297039825</v>
+        <v>0.2061256472858269</v>
       </c>
       <c r="G84">
-        <v>1.12167529614528</v>
+        <v>1.324704148300631</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="O84">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="85">
@@ -5667,22 +5667,22 @@
         </is>
       </c>
       <c r="B85">
-        <v>0.6396026014765602</v>
+        <v>0.6157807813097967</v>
       </c>
       <c r="C85">
-        <v>0.4382430252396978</v>
+        <v>0.4369321038536699</v>
       </c>
       <c r="D85">
-        <v>-1.019772603196488</v>
+        <v>-1.109701596672877</v>
       </c>
       <c r="E85">
-        <v>0.3078363193484738</v>
+        <v>0.2671276346463584</v>
       </c>
       <c r="F85">
-        <v>0.2709424677876159</v>
+        <v>0.2615223735766521</v>
       </c>
       <c r="G85">
-        <v>1.509883227815946</v>
+        <v>1.449917899737035</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="O85">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="86">
@@ -5730,22 +5730,22 @@
         </is>
       </c>
       <c r="B86">
-        <v>0.996492855463358</v>
+        <v>1.020427252062265</v>
       </c>
       <c r="C86">
-        <v>0.03720308076397406</v>
+        <v>0.04157947594902758</v>
       </c>
       <c r="D86">
-        <v>-0.09443596909694545</v>
+        <v>0.4863316264099739</v>
       </c>
       <c r="E86">
-        <v>0.924762844257879</v>
+        <v>0.6267320593228447</v>
       </c>
       <c r="F86">
-        <v>0.926417754410041</v>
+        <v>0.9405665606452783</v>
       </c>
       <c r="G86">
-        <v>1.071868502371131</v>
+        <v>1.107068675753237</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="O86">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="87">
@@ -5793,22 +5793,22 @@
         </is>
       </c>
       <c r="B87">
-        <v>0.9559567761782271</v>
+        <v>0.929394257172193</v>
       </c>
       <c r="C87">
-        <v>0.04394726064697838</v>
+        <v>0.04376642150444696</v>
       </c>
       <c r="D87">
-        <v>-1.024923499041156</v>
+        <v>-1.673023265406108</v>
       </c>
       <c r="E87">
-        <v>0.3053992857083074</v>
+        <v>0.09432271606937177</v>
       </c>
       <c r="F87">
-        <v>0.8770619695772618</v>
+        <v>0.8529939268228648</v>
       </c>
       <c r="G87">
-        <v>1.041948447909035</v>
+        <v>1.012637555910789</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="O87">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="88">
@@ -5856,22 +5856,22 @@
         </is>
       </c>
       <c r="B88">
-        <v>0.9486551777876736</v>
+        <v>0.9710573776846128</v>
       </c>
       <c r="C88">
-        <v>0.04327246310480794</v>
+        <v>0.04143679136619195</v>
       </c>
       <c r="D88">
-        <v>-1.218093351890329</v>
+        <v>-0.7087836711054087</v>
       </c>
       <c r="E88">
-        <v>0.2231884999553571</v>
+        <v>0.4784587323462446</v>
       </c>
       <c r="F88">
-        <v>0.8715148550065622</v>
+        <v>0.8953108166555971</v>
       </c>
       <c r="G88">
-        <v>1.032623415623348</v>
+        <v>1.053212374087117</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="O88">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="89">
@@ -5919,22 +5919,22 @@
         </is>
       </c>
       <c r="B89">
-        <v>0.9925380314186959</v>
+        <v>0.97868562666188</v>
       </c>
       <c r="C89">
-        <v>0.03608217072819587</v>
+        <v>0.04000256588644131</v>
       </c>
       <c r="D89">
-        <v>-0.2075803144325896</v>
+        <v>-0.5385855715493275</v>
       </c>
       <c r="E89">
-        <v>0.8355566763626804</v>
+        <v>0.5901728455005263</v>
       </c>
       <c r="F89">
-        <v>0.9247704786426753</v>
+        <v>0.9048841149701655</v>
       </c>
       <c r="G89">
-        <v>1.06527161772986</v>
+        <v>1.058506321404633</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="O89">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="90">
@@ -5982,22 +5982,22 @@
         </is>
       </c>
       <c r="B90">
-        <v>0.9319200330385602</v>
+        <v>1.221553860905619</v>
       </c>
       <c r="C90">
-        <v>0.4237889655876448</v>
+        <v>0.4489068486616338</v>
       </c>
       <c r="D90">
-        <v>-0.1663758973542507</v>
+        <v>0.4458022982038808</v>
       </c>
       <c r="E90">
-        <v>0.8678611407105252</v>
+        <v>0.6557400615628214</v>
       </c>
       <c r="F90">
-        <v>0.4061148088097093</v>
+        <v>0.5067601060501465</v>
       </c>
       <c r="G90">
-        <v>2.138496132470577</v>
+        <v>2.944576373077332</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="O90">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="91">
@@ -6045,22 +6045,22 @@
         </is>
       </c>
       <c r="B91">
-        <v>0.5773315215255466</v>
+        <v>0.4308995201532797</v>
       </c>
       <c r="C91">
-        <v>0.4461270921054593</v>
+        <v>0.4605996814001371</v>
       </c>
       <c r="D91">
-        <v>-1.231350049097959</v>
+        <v>-1.827791859068676</v>
       </c>
       <c r="E91">
-        <v>0.2181919705091927</v>
+        <v>0.06758079548798651</v>
       </c>
       <c r="F91">
-        <v>0.2408137056966595</v>
+        <v>0.17470802364066</v>
       </c>
       <c r="G91">
-        <v>1.384105961837812</v>
+        <v>1.062769714859933</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="O91">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="92">
@@ -6108,22 +6108,22 @@
         </is>
       </c>
       <c r="B92">
-        <v>0.5983784861909636</v>
+        <v>0.7328140779704971</v>
       </c>
       <c r="C92">
-        <v>0.4424787244630804</v>
+        <v>0.4531570907664245</v>
       </c>
       <c r="D92">
-        <v>-1.160579654563702</v>
+        <v>-0.6859944618249387</v>
       </c>
       <c r="E92">
-        <v>0.2458128832734374</v>
+        <v>0.4927166007638971</v>
       </c>
       <c r="F92">
-        <v>0.2513838640981217</v>
+        <v>0.3014850553082435</v>
       </c>
       <c r="G92">
-        <v>1.424342863137906</v>
+        <v>1.781237455776025</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="O92">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="93">
@@ -6171,22 +6171,22 @@
         </is>
       </c>
       <c r="B93">
-        <v>0.7893676839487831</v>
+        <v>0.6897938919061797</v>
       </c>
       <c r="C93">
-        <v>0.4094277266395517</v>
+        <v>0.4308408968512673</v>
       </c>
       <c r="D93">
-        <v>-0.5776918334729364</v>
+        <v>-0.8619479629467869</v>
       </c>
       <c r="E93">
-        <v>0.5634721936937084</v>
+        <v>0.3887161538448774</v>
       </c>
       <c r="F93">
-        <v>0.3538130358928032</v>
+        <v>0.296474201546684</v>
       </c>
       <c r="G93">
-        <v>1.76110339996475</v>
+        <v>1.604914056025041</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="O93">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="94">
@@ -6234,22 +6234,22 @@
         </is>
       </c>
       <c r="B94">
-        <v>0.8832351197064066</v>
+        <v>1.02046861220264</v>
       </c>
       <c r="C94">
-        <v>0.2480696291525108</v>
+        <v>0.2699883155517628</v>
       </c>
       <c r="D94">
-        <v>-0.5005201181367156</v>
+        <v>0.0750474904074325</v>
       </c>
       <c r="E94">
-        <v>0.6167088939616998</v>
+        <v>0.9401769265197791</v>
       </c>
       <c r="F94">
-        <v>0.5431491174991259</v>
+        <v>0.6011532235881218</v>
       </c>
       <c r="G94">
-        <v>1.436261703369233</v>
+        <v>1.732264167652978</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="O94">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="95">
@@ -6297,22 +6297,22 @@
         </is>
       </c>
       <c r="B95">
-        <v>0.7290025426615386</v>
+        <v>0.6029583592116198</v>
       </c>
       <c r="C95">
-        <v>0.2788629704560729</v>
+        <v>0.2832062279022103</v>
       </c>
       <c r="D95">
-        <v>-1.133452959303682</v>
+        <v>-1.786355986662534</v>
       </c>
       <c r="E95">
-        <v>0.2570240849497324</v>
+        <v>0.0740416371981641</v>
       </c>
       <c r="F95">
-        <v>0.4220466450251962</v>
+        <v>0.3461160527608606</v>
       </c>
       <c r="G95">
-        <v>1.25920846302489</v>
+        <v>1.050395611654452</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="O95">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="96">
@@ -6360,22 +6360,22 @@
         </is>
       </c>
       <c r="B96">
-        <v>0.6343505610281401</v>
+        <v>0.7241013184501577</v>
       </c>
       <c r="C96">
-        <v>0.276502519319284</v>
+        <v>0.2729791524778999</v>
       </c>
       <c r="D96">
-        <v>-1.646109927324591</v>
+        <v>-1.182595633572768</v>
       </c>
       <c r="E96">
-        <v>0.09974112894276635</v>
+        <v>0.2369694438437516</v>
       </c>
       <c r="F96">
-        <v>0.3689520749790268</v>
+        <v>0.4240714765606303</v>
       </c>
       <c r="G96">
-        <v>1.090658276686995</v>
+        <v>1.236401758575463</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="O96">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="97">
@@ -6423,22 +6423,22 @@
         </is>
       </c>
       <c r="B97">
-        <v>0.9334642354514573</v>
+        <v>0.8712642264864066</v>
       </c>
       <c r="C97">
-        <v>0.237744351316886</v>
+        <v>0.2577344618495573</v>
       </c>
       <c r="D97">
-        <v>-0.2896078441846564</v>
+        <v>-0.5346975613175242</v>
       </c>
       <c r="E97">
-        <v>0.7721162652812623</v>
+        <v>0.5928590080987074</v>
       </c>
       <c r="F97">
-        <v>0.585772965618523</v>
+        <v>0.5257338141841839</v>
       </c>
       <c r="G97">
-        <v>1.487531057270459</v>
+        <v>1.443889154310731</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="O97">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="98">
@@ -6486,22 +6486,22 @@
         </is>
       </c>
       <c r="B98">
-        <v>0.8386640308440194</v>
+        <v>0.8657676627515399</v>
       </c>
       <c r="C98">
-        <v>0.1492291058510298</v>
+        <v>0.1495392036806912</v>
       </c>
       <c r="D98">
-        <v>-1.179026649689137</v>
+        <v>-0.963885661307032</v>
       </c>
       <c r="E98">
-        <v>0.2383875642104948</v>
+        <v>0.3351032533923756</v>
       </c>
       <c r="F98">
-        <v>0.6259850652337041</v>
+        <v>0.6458227796637663</v>
       </c>
       <c r="G98">
-        <v>1.123600858383016</v>
+        <v>1.160618159453129</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="O98">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="99">
@@ -6549,22 +6549,22 @@
         </is>
       </c>
       <c r="B99">
-        <v>0.804789879417803</v>
+        <v>0.7430537459991495</v>
       </c>
       <c r="C99">
-        <v>0.1209569540337797</v>
+        <v>0.1394058625967661</v>
       </c>
       <c r="D99">
-        <v>-1.795465640868992</v>
+        <v>-2.130375974696013</v>
       </c>
       <c r="E99">
-        <v>0.07257954231127875</v>
+        <v>0.03314058567568486</v>
       </c>
       <c r="F99">
-        <v>0.6349269484122786</v>
+        <v>0.5654025236070855</v>
       </c>
       <c r="G99">
-        <v>1.020096487687207</v>
+        <v>0.9765235321571696</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="O99">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="100">
@@ -6612,22 +6612,22 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.9237976428298476</v>
+        <v>0.9249295180074435</v>
       </c>
       <c r="C100">
-        <v>0.1381809813780774</v>
+        <v>0.1641595568553217</v>
       </c>
       <c r="D100">
-        <v>-0.5736117358600976</v>
+        <v>-0.4753773865893053</v>
       </c>
       <c r="E100">
-        <v>0.5662305683340276</v>
+        <v>0.6345180095375322</v>
       </c>
       <c r="F100">
-        <v>0.704623275883266</v>
+        <v>0.6704644751586574</v>
       </c>
       <c r="G100">
-        <v>1.211146600044141</v>
+        <v>1.275973067893029</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="O100">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="101">
@@ -6675,22 +6675,22 @@
         </is>
       </c>
       <c r="B101">
-        <v>0.8876059316594888</v>
+        <v>0.8548787719752168</v>
       </c>
       <c r="C101">
-        <v>0.1396324006977447</v>
+        <v>0.1363498390735512</v>
       </c>
       <c r="D101">
-        <v>-0.853866327179454</v>
+        <v>-1.149950805420722</v>
       </c>
       <c r="E101">
-        <v>0.3931790588152205</v>
+        <v>0.2501641337436446</v>
       </c>
       <c r="F101">
-        <v>0.675094983588736</v>
+        <v>0.6544000736527184</v>
       </c>
       <c r="G101">
-        <v>1.167012507971855</v>
+        <v>1.116775110819578</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="O101">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="102">
@@ -6738,22 +6738,22 @@
         </is>
       </c>
       <c r="B102">
-        <v>0.1698095453876536</v>
+        <v>0.2213860210850722</v>
       </c>
       <c r="C102">
-        <v>0.983075655322301</v>
+        <v>0.9939807221485749</v>
       </c>
       <c r="D102">
-        <v>-1.803602582985971</v>
+        <v>-1.516978514605464</v>
       </c>
       <c r="E102">
-        <v>0.07129363086913292</v>
+        <v>0.1292721086843879</v>
       </c>
       <c r="F102">
-        <v>0.02472672417772231</v>
+        <v>0.03155529686377445</v>
       </c>
       <c r="G102">
-        <v>1.166158586050833</v>
+        <v>1.553202638006098</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="O102">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="103">
@@ -6801,22 +6801,22 @@
         </is>
       </c>
       <c r="B103">
-        <v>0.205502146892913</v>
+        <v>0.1260933904981573</v>
       </c>
       <c r="C103">
-        <v>0.7919055861948416</v>
+        <v>0.9357617937692524</v>
       </c>
       <c r="D103">
-        <v>-1.998090208627027</v>
+        <v>-2.212884161265932</v>
       </c>
       <c r="E103">
-        <v>0.04570688107952537</v>
+        <v>0.02690563293709675</v>
       </c>
       <c r="F103">
-        <v>0.04352563404621819</v>
+        <v>0.02014514694406275</v>
       </c>
       <c r="G103">
-        <v>0.9702588670564288</v>
+        <v>0.7892493001649098</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="O103">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="104">
@@ -6864,22 +6864,22 @@
         </is>
       </c>
       <c r="B104">
-        <v>0.3759806786855453</v>
+        <v>0.3264204147689848</v>
       </c>
       <c r="C104">
-        <v>0.8680198899218693</v>
+        <v>1.056213533351837</v>
       </c>
       <c r="D104">
-        <v>-1.12695288984131</v>
+        <v>-1.059983684404279</v>
       </c>
       <c r="E104">
-        <v>0.2597623996920791</v>
+        <v>0.2891520219971284</v>
       </c>
       <c r="F104">
-        <v>0.06859708447633239</v>
+        <v>0.04118382907090228</v>
       </c>
       <c r="G104">
-        <v>2.060750421450001</v>
+        <v>2.587187485518128</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="O104">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="105">
@@ -6927,22 +6927,22 @@
         </is>
       </c>
       <c r="B105">
-        <v>0.2673816046279803</v>
+        <v>0.2664097623400104</v>
       </c>
       <c r="C105">
-        <v>0.9180739358382729</v>
+        <v>0.8977750450309833</v>
       </c>
       <c r="D105">
-        <v>-1.436788867052742</v>
+        <v>-1.473330878250489</v>
       </c>
       <c r="E105">
-        <v>0.1507779947045744</v>
+        <v>0.1406618384644878</v>
       </c>
       <c r="F105">
-        <v>0.04422476911977173</v>
+        <v>0.0458524590121322</v>
       </c>
       <c r="G105">
-        <v>1.616581022725362</v>
+        <v>1.547881247792656</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="O105">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="106">
@@ -6990,22 +6990,22 @@
         </is>
       </c>
       <c r="B106">
-        <v>0.2510417326387798</v>
+        <v>0.2943694548550703</v>
       </c>
       <c r="C106">
-        <v>0.8526489243133478</v>
+        <v>0.8531945886892135</v>
       </c>
       <c r="D106">
-        <v>-1.620990830769931</v>
+        <v>-1.433342015539568</v>
       </c>
       <c r="E106">
-        <v>0.1050196051853453</v>
+        <v>0.1517601203511784</v>
       </c>
       <c r="F106">
-        <v>0.04720302632982376</v>
+        <v>0.05529071333393965</v>
       </c>
       <c r="G106">
-        <v>1.335125232986643</v>
+        <v>1.567232012875479</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="O106">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="107">
@@ -7053,22 +7053,22 @@
         </is>
       </c>
       <c r="B107">
-        <v>0.2532997614841665</v>
+        <v>0.1546236768100691</v>
       </c>
       <c r="C107">
-        <v>0.6823071757026014</v>
+        <v>0.8067067296885065</v>
       </c>
       <c r="D107">
-        <v>-2.012556385904478</v>
+        <v>-2.314051608866039</v>
       </c>
       <c r="E107">
-        <v>0.04416131915188332</v>
+        <v>0.02066489138227803</v>
       </c>
       <c r="F107">
-        <v>0.06650493294954765</v>
+        <v>0.03181309943831227</v>
       </c>
       <c r="G107">
-        <v>0.9647520315013269</v>
+        <v>0.7515294596373689</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="O107">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="108">
@@ -7116,22 +7116,22 @@
         </is>
       </c>
       <c r="B108">
-        <v>0.4806930066362318</v>
+        <v>0.4390419659090566</v>
       </c>
       <c r="C108">
-        <v>0.7717389207246708</v>
+        <v>0.926230032001207</v>
       </c>
       <c r="D108">
-        <v>-0.9491894639598991</v>
+        <v>-0.8887212114807245</v>
       </c>
       <c r="E108">
-        <v>0.3425242592191121</v>
+        <v>0.3741529284201189</v>
       </c>
       <c r="F108">
-        <v>0.1059162128160861</v>
+        <v>0.07146569173805041</v>
       </c>
       <c r="G108">
-        <v>2.181590150227568</v>
+        <v>2.697208172780608</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="O108">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="109">
@@ -7179,22 +7179,22 @@
         </is>
       </c>
       <c r="B109">
-        <v>0.4020041963080057</v>
+        <v>0.3390285799832226</v>
       </c>
       <c r="C109">
-        <v>0.7903857269716481</v>
+        <v>0.7796715500498083</v>
       </c>
       <c r="D109">
-        <v>-1.15297217642337</v>
+        <v>-1.387341718895641</v>
       </c>
       <c r="E109">
-        <v>0.2489218049327784</v>
+        <v>0.1653375874756335</v>
       </c>
       <c r="F109">
-        <v>0.08539904929732459</v>
+        <v>0.07354932375840291</v>
       </c>
       <c r="G109">
-        <v>1.892379074228271</v>
+        <v>1.562765939534673</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="O109">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="110">
@@ -7242,22 +7242,22 @@
         </is>
       </c>
       <c r="B110">
-        <v>0.9718610465775636</v>
+        <v>0.9975786497376853</v>
       </c>
       <c r="C110">
-        <v>0.04795508945043182</v>
+        <v>0.05608090337542404</v>
       </c>
       <c r="D110">
-        <v>-0.5951910686421241</v>
+        <v>-0.0432283776763908</v>
       </c>
       <c r="E110">
-        <v>0.5517157597105127</v>
+        <v>0.9655194841121083</v>
       </c>
       <c r="F110">
-        <v>0.8846769851453401</v>
+        <v>0.8937395857872267</v>
       </c>
       <c r="G110">
-        <v>1.067637012959783</v>
+        <v>1.113482247220705</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="O110">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="111">
@@ -7305,22 +7305,22 @@
         </is>
       </c>
       <c r="B111">
-        <v>0.9356330079007182</v>
+        <v>0.9073731297574626</v>
       </c>
       <c r="C111">
-        <v>0.05780905223352977</v>
+        <v>0.05991358152802724</v>
       </c>
       <c r="D111">
-        <v>-1.15089181357931</v>
+        <v>-1.622362109850027</v>
       </c>
       <c r="E111">
-        <v>0.2497767460924759</v>
+        <v>0.1047258370778085</v>
       </c>
       <c r="F111">
-        <v>0.8354075199659754</v>
+        <v>0.806839926604016</v>
       </c>
       <c r="G111">
-        <v>1.04788274530854</v>
+        <v>1.020432888182947</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="O111">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="112">
@@ -7368,22 +7368,22 @@
         </is>
       </c>
       <c r="B112">
-        <v>0.9969756252543286</v>
+        <v>1.032356369219743</v>
       </c>
       <c r="C112">
-        <v>0.05840629592362021</v>
+        <v>0.05752035108540428</v>
       </c>
       <c r="D112">
-        <v>-0.05186011818075976</v>
+        <v>0.5536114759553781</v>
       </c>
       <c r="E112">
-        <v>0.9586401525702095</v>
+        <v>0.5798447704660098</v>
       </c>
       <c r="F112">
-        <v>0.8891376719341866</v>
+        <v>0.9222915505687942</v>
       </c>
       <c r="G112">
-        <v>1.117892570212492</v>
+        <v>1.155556149691815</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="O112">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="113">
@@ -7431,22 +7431,22 @@
         </is>
       </c>
       <c r="B113">
-        <v>0.9854426667144179</v>
+        <v>0.9580815745813251</v>
       </c>
       <c r="C113">
-        <v>0.04625040689064311</v>
+        <v>0.05388013166796429</v>
       </c>
       <c r="D113">
-        <v>-0.3170638253254626</v>
+        <v>-0.7947707696844352</v>
       </c>
       <c r="E113">
-        <v>0.7511951729979174</v>
+        <v>0.4267468571191587</v>
       </c>
       <c r="F113">
-        <v>0.9000423486515193</v>
+        <v>0.8620642533321379</v>
       </c>
       <c r="G113">
-        <v>1.078946174961835</v>
+        <v>1.064793372424611</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         </is>
       </c>
       <c r="O113">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="114">
@@ -7494,22 +7494,22 @@
         </is>
       </c>
       <c r="B114">
-        <v>0.6547778567669311</v>
+        <v>0.8165828423198053</v>
       </c>
       <c r="C114">
-        <v>0.563998216301646</v>
+        <v>0.6181038518642989</v>
       </c>
       <c r="D114">
-        <v>-0.7508166490705962</v>
+        <v>-0.3278201726550595</v>
       </c>
       <c r="E114">
-        <v>0.4527630081944143</v>
+        <v>0.7430476338548813</v>
       </c>
       <c r="F114">
-        <v>0.2167793111724733</v>
+        <v>0.2431472140849401</v>
       </c>
       <c r="G114">
-        <v>1.9777442754728</v>
+        <v>2.742402543580665</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="O114">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="115">
@@ -7557,22 +7557,22 @@
         </is>
       </c>
       <c r="B115">
-        <v>0.5440645935756738</v>
+        <v>0.4139119788364118</v>
       </c>
       <c r="C115">
-        <v>0.6010130182267757</v>
+        <v>0.63160395259102</v>
       </c>
       <c r="D115">
-        <v>-1.012768912693946</v>
+        <v>-1.396606109967283</v>
       </c>
       <c r="E115">
-        <v>0.3111705528304082</v>
+        <v>0.162532051932595</v>
       </c>
       <c r="F115">
-        <v>0.1675202279800122</v>
+        <v>0.1200288751567572</v>
       </c>
       <c r="G115">
-        <v>1.766988294798532</v>
+        <v>1.427349260755189</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="O115">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="116">
@@ -7620,22 +7620,22 @@
         </is>
       </c>
       <c r="B116">
-        <v>1.020964682300759</v>
+        <v>1.333088463806502</v>
       </c>
       <c r="C116">
-        <v>0.6239937402025729</v>
+        <v>0.6221470290226467</v>
       </c>
       <c r="D116">
-        <v>0.03325024910536485</v>
+        <v>0.4621068493924637</v>
       </c>
       <c r="E116">
-        <v>0.9734750272617764</v>
+        <v>0.6440046986005215</v>
       </c>
       <c r="F116">
-        <v>0.3005150899663282</v>
+        <v>0.3938097451917275</v>
       </c>
       <c r="G116">
-        <v>3.468607458687961</v>
+        <v>4.512648236952034</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="O116">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="117">
@@ -7683,22 +7683,22 @@
         </is>
       </c>
       <c r="B117">
-        <v>0.8421549587918015</v>
+        <v>0.6902345401213671</v>
       </c>
       <c r="C117">
-        <v>0.5418731119813784</v>
+        <v>0.5835735489591104</v>
       </c>
       <c r="D117">
-        <v>-0.3170322374447886</v>
+        <v>-0.6352649577591556</v>
       </c>
       <c r="E117">
-        <v>0.751219141065913</v>
+        <v>0.5252556240578261</v>
       </c>
       <c r="F117">
-        <v>0.2911714445468666</v>
+        <v>0.2199165848682083</v>
       </c>
       <c r="G117">
-        <v>2.435764179146575</v>
+        <v>2.166383770746834</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="O117">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="118">
@@ -7746,22 +7746,22 @@
         </is>
       </c>
       <c r="B118">
-        <v>0.6867123625745039</v>
+        <v>0.769387411223269</v>
       </c>
       <c r="C118">
-        <v>0.3292362102014291</v>
+        <v>0.3751144187670963</v>
       </c>
       <c r="D118">
-        <v>-1.141550500816004</v>
+        <v>-0.6988818277623243</v>
       </c>
       <c r="E118">
-        <v>0.2536409091434939</v>
+        <v>0.4846258850204183</v>
       </c>
       <c r="F118">
-        <v>0.3601873828460767</v>
+        <v>0.3688477205799536</v>
       </c>
       <c r="G118">
-        <v>1.309245940783496</v>
+        <v>1.604881785952444</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="O118">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="119">
@@ -7809,22 +7809,22 @@
         </is>
       </c>
       <c r="B119">
-        <v>0.6607809161655234</v>
+        <v>0.5481203967304542</v>
       </c>
       <c r="C119">
-        <v>0.3756298666904089</v>
+        <v>0.3950267021311524</v>
       </c>
       <c r="D119">
-        <v>-1.103035125342362</v>
+        <v>-1.522075117602022</v>
       </c>
       <c r="E119">
-        <v>0.2700119116728487</v>
+        <v>0.1279902598594038</v>
       </c>
       <c r="F119">
-        <v>0.3164614178621193</v>
+        <v>0.2527136060822713</v>
       </c>
       <c r="G119">
-        <v>1.379730338435084</v>
+        <v>1.18883970661296</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         </is>
       </c>
       <c r="O119">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="120">
@@ -7872,22 +7872,22 @@
         </is>
       </c>
       <c r="B120">
-        <v>0.816925058195423</v>
+        <v>0.9959444875890063</v>
       </c>
       <c r="C120">
-        <v>0.3870462028961194</v>
+        <v>0.3863414001160071</v>
       </c>
       <c r="D120">
-        <v>-0.5224387033158853</v>
+        <v>-0.01051856803851285</v>
       </c>
       <c r="E120">
-        <v>0.6013649143706674</v>
+        <v>0.9916075517177305</v>
       </c>
       <c r="F120">
-        <v>0.3825849593646023</v>
+        <v>0.4670686694806404</v>
       </c>
       <c r="G120">
-        <v>1.744361701557632</v>
+        <v>2.123682206005989</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="O120">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="121">
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="B121">
-        <v>0.974888081485524</v>
+        <v>0.8595439817121682</v>
       </c>
       <c r="C121">
-        <v>0.3106628389442793</v>
+        <v>0.3540885481671536</v>
       </c>
       <c r="D121">
-        <v>-0.08186560993057454</v>
+        <v>-0.4274447309164887</v>
       </c>
       <c r="E121">
-        <v>0.9347535819128061</v>
+        <v>0.6690554329547556</v>
       </c>
       <c r="F121">
-        <v>0.5302956602442629</v>
+        <v>0.4294052849158937</v>
       </c>
       <c r="G121">
-        <v>1.792220534078579</v>
+        <v>1.720556039831503</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         </is>
       </c>
       <c r="O121">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="122">
@@ -7998,22 +7998,22 @@
         </is>
       </c>
       <c r="B122">
-        <v>0.9040753076156572</v>
+        <v>0.876526952127813</v>
       </c>
       <c r="C122">
-        <v>0.07394621912393454</v>
+        <v>0.07386229223573558</v>
       </c>
       <c r="D122">
-        <v>-1.36372918547776</v>
+        <v>-1.784236873600113</v>
       </c>
       <c r="E122">
-        <v>0.1726528149353239</v>
+        <v>0.07438518295080083</v>
       </c>
       <c r="F122">
-        <v>0.7820985342863066</v>
+        <v>0.7583917107849354</v>
       </c>
       <c r="G122">
-        <v>1.045075685490459</v>
+        <v>1.013064207955653</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="O122">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="123">
@@ -8061,22 +8061,22 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.924177281678647</v>
+        <v>0.9197511523965918</v>
       </c>
       <c r="C123">
-        <v>0.04263359872478144</v>
+        <v>0.03981647662990895</v>
       </c>
       <c r="D123">
-        <v>-1.849512234805717</v>
+        <v>-2.10094260298602</v>
       </c>
       <c r="E123">
-        <v>0.0643838827916605</v>
+        <v>0.03564600501278543</v>
       </c>
       <c r="F123">
-        <v>0.850091166547675</v>
+        <v>0.8507040380798669</v>
       </c>
       <c r="G123">
-        <v>1.004720060131378</v>
+        <v>0.9944024531072446</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="O123">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="124">
@@ -8124,22 +8124,22 @@
         </is>
       </c>
       <c r="B124">
-        <v>0.9661730151877085</v>
+        <v>0.9575703093746909</v>
       </c>
       <c r="C124">
-        <v>0.07223729918544829</v>
+        <v>0.07127205035188861</v>
       </c>
       <c r="D124">
-        <v>-0.4763793282115293</v>
+        <v>-0.6083188325971035</v>
       </c>
       <c r="E124">
-        <v>0.6338041590578698</v>
+        <v>0.5429760329168303</v>
       </c>
       <c r="F124">
-        <v>0.8386222931722609</v>
+        <v>0.8327291978712442</v>
       </c>
       <c r="G124">
-        <v>1.113123634891447</v>
+        <v>1.101127352973779</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="O124">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="125">
@@ -8187,22 +8187,22 @@
         </is>
       </c>
       <c r="B125">
-        <v>0.423311973506633</v>
+        <v>0.3139158246850947</v>
       </c>
       <c r="C125">
-        <v>0.5156961009532688</v>
+        <v>0.5470558026193205</v>
       </c>
       <c r="D125">
-        <v>-1.666962081282081</v>
+        <v>-2.117938239053384</v>
       </c>
       <c r="E125">
-        <v>0.09552194501162758</v>
+        <v>0.03418029858447304</v>
       </c>
       <c r="F125">
-        <v>0.1540633140922613</v>
+        <v>0.1074381362368799</v>
       </c>
       <c r="G125">
-        <v>1.163112892708319</v>
+        <v>0.9172082506201978</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="O125">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="126">
@@ -8250,22 +8250,22 @@
         </is>
       </c>
       <c r="B126">
-        <v>0.6199910508990082</v>
+        <v>0.544838694792199</v>
       </c>
       <c r="C126">
-        <v>0.2576523132721386</v>
+        <v>0.2523292930434567</v>
       </c>
       <c r="D126">
-        <v>-1.855408278737638</v>
+        <v>-2.406638934629241</v>
       </c>
       <c r="E126">
-        <v>0.06353794607569446</v>
+        <v>0.01610007874824734</v>
       </c>
       <c r="F126">
-        <v>0.3741720765593486</v>
+        <v>0.3322652020455969</v>
       </c>
       <c r="G126">
-        <v>1.02730515523621</v>
+        <v>0.8934104489886673</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="O126">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="127">
@@ -8313,22 +8313,22 @@
         </is>
       </c>
       <c r="B127">
-        <v>0.6162785175444</v>
+        <v>0.5321714487635403</v>
       </c>
       <c r="C127">
-        <v>0.4991087032847636</v>
+        <v>0.5201781374735761</v>
       </c>
       <c r="D127">
-        <v>-0.9698413904147891</v>
+        <v>-1.212641447237141</v>
       </c>
       <c r="E127">
-        <v>0.3321255579979319</v>
+        <v>0.2252669351608937</v>
       </c>
       <c r="F127">
-        <v>0.2317047466486482</v>
+        <v>0.1919884654691635</v>
       </c>
       <c r="G127">
-        <v>1.639151621536015</v>
+        <v>1.475122217300981</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="O127">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="128">
@@ -8376,22 +8376,22 @@
         </is>
       </c>
       <c r="B128">
-        <v>0.471203424481838</v>
+        <v>0.3616442095082134</v>
       </c>
       <c r="C128">
-        <v>0.4395216247293247</v>
+        <v>0.4599717426959116</v>
       </c>
       <c r="D128">
-        <v>-1.712009914321078</v>
+        <v>-2.21121060865178</v>
       </c>
       <c r="E128">
-        <v>0.08689484139993243</v>
+        <v>0.02702125609277064</v>
       </c>
       <c r="F128">
-        <v>0.1991071943936251</v>
+        <v>0.1468090602004682</v>
       </c>
       <c r="G128">
-        <v>1.115141358500907</v>
+        <v>0.8908614638104159</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="O128">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="129">
@@ -8439,22 +8439,22 @@
         </is>
       </c>
       <c r="B129">
-        <v>0.6334690566825534</v>
+        <v>0.5807525782284985</v>
       </c>
       <c r="C129">
-        <v>0.2400420323326924</v>
+        <v>0.2345396917124972</v>
       </c>
       <c r="D129">
-        <v>-1.901934094595741</v>
+        <v>-2.317008536562665</v>
       </c>
       <c r="E129">
-        <v>0.05717977118956011</v>
+        <v>0.0205032667526581</v>
       </c>
       <c r="F129">
-        <v>0.3957320795174332</v>
+        <v>0.3667335132698535</v>
       </c>
       <c r="G129">
-        <v>1.014027081816617</v>
+        <v>0.9196693100444088</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="O129">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="130">
@@ -8502,22 +8502,22 @@
         </is>
       </c>
       <c r="B130">
-        <v>0.6984084947048542</v>
+        <v>0.6129111919994301</v>
       </c>
       <c r="C130">
-        <v>0.4239197603776133</v>
+        <v>0.4367784648777006</v>
       </c>
       <c r="D130">
-        <v>-0.8467430513665285</v>
+        <v>-1.120786090192174</v>
       </c>
       <c r="E130">
-        <v>0.3971383568086217</v>
+        <v>0.2623789264066959</v>
       </c>
       <c r="F130">
-        <v>0.3042764626868613</v>
+        <v>0.2603820539374821</v>
       </c>
       <c r="G130">
-        <v>1.603063283859329</v>
+        <v>1.442726653382796</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="O130">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="131">
@@ -8565,22 +8565,22 @@
         </is>
       </c>
       <c r="B131">
-        <v>0.9533641541166635</v>
+        <v>0.9434641332743449</v>
       </c>
       <c r="C131">
-        <v>0.03247923995262914</v>
+        <v>0.03079641468840485</v>
       </c>
       <c r="D131">
-        <v>-1.470426491986478</v>
+        <v>-1.889730672629542</v>
       </c>
       <c r="E131">
-        <v>0.1414462807520629</v>
+        <v>0.05879398967965889</v>
       </c>
       <c r="F131">
-        <v>0.894566106542784</v>
+        <v>0.88820137052759</v>
       </c>
       <c r="G131">
-        <v>1.016026880190225</v>
+        <v>1.002165275028092</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="O131">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="132">
@@ -8628,22 +8628,22 @@
         </is>
       </c>
       <c r="B132">
-        <v>0.9515751236145189</v>
+        <v>0.9550439703290967</v>
       </c>
       <c r="C132">
-        <v>0.02633958222222048</v>
+        <v>0.02412400640748712</v>
       </c>
       <c r="D132">
-        <v>-1.884488604153316</v>
+        <v>-1.906727122971628</v>
       </c>
       <c r="E132">
-        <v>0.05949891483389029</v>
+        <v>0.05655593279790683</v>
       </c>
       <c r="F132">
-        <v>0.9036968885797301</v>
+        <v>0.9109383279968711</v>
       </c>
       <c r="G132">
-        <v>1.001989967349653</v>
+        <v>1.001285111438518</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="O132">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="133">
@@ -8691,22 +8691,22 @@
         </is>
       </c>
       <c r="B133">
-        <v>0.9907002732937646</v>
+        <v>0.9918821762667891</v>
       </c>
       <c r="C133">
-        <v>0.03076695207613247</v>
+        <v>0.02872261791461703</v>
       </c>
       <c r="D133">
-        <v>-0.3036777618015302</v>
+        <v>-0.2837816768751117</v>
       </c>
       <c r="E133">
-        <v>0.7613734018810503</v>
+        <v>0.7765776972435101</v>
       </c>
       <c r="F133">
-        <v>0.932724545370046</v>
+        <v>0.9375865088103168</v>
       </c>
       <c r="G133">
-        <v>1.052279621434159</v>
+        <v>1.049322107721135</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="O133">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="134">
@@ -8754,22 +8754,22 @@
         </is>
       </c>
       <c r="B134">
-        <v>0.5644270561441748</v>
+        <v>0.4670941620797316</v>
       </c>
       <c r="C134">
-        <v>0.4225719301772083</v>
+        <v>0.42227233217571</v>
       </c>
       <c r="D134">
-        <v>-1.353483469723797</v>
+        <v>-1.802685972471153</v>
       </c>
       <c r="E134">
-        <v>0.1759012274277661</v>
+        <v>0.07143754642738818</v>
       </c>
       <c r="F134">
-        <v>0.2465550740568752</v>
+        <v>0.2041576126317915</v>
       </c>
       <c r="G134">
-        <v>1.292116590689551</v>
+        <v>1.068669218044099</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="O134">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="135">
@@ -8817,22 +8817,22 @@
         </is>
       </c>
       <c r="B135">
-        <v>0.6346485573611614</v>
+        <v>0.6151040444316614</v>
       </c>
       <c r="C135">
-        <v>0.2478568144169425</v>
+        <v>0.2350222228096295</v>
       </c>
       <c r="D135">
-        <v>-1.834461914413051</v>
+        <v>-2.067735730423108</v>
       </c>
       <c r="E135">
-        <v>0.06658545626375083</v>
+        <v>0.03866488010302133</v>
       </c>
       <c r="F135">
-        <v>0.3904425983164543</v>
+        <v>0.3880585922445316</v>
       </c>
       <c r="G135">
-        <v>1.031595407615208</v>
+        <v>0.9749893264514337</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="O135">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="136">
@@ -8880,22 +8880,22 @@
         </is>
       </c>
       <c r="B136">
-        <v>0.7855141145637667</v>
+        <v>0.7380384212652947</v>
       </c>
       <c r="C136">
-        <v>0.408679639971556</v>
+        <v>0.4023704126736846</v>
       </c>
       <c r="D136">
-        <v>-0.5907239532995752</v>
+        <v>-0.7549247778515582</v>
       </c>
       <c r="E136">
-        <v>0.5547053957868442</v>
+        <v>0.4502941177731628</v>
       </c>
       <c r="F136">
-        <v>0.3526023909542493</v>
+        <v>0.3354135899811125</v>
       </c>
       <c r="G136">
-        <v>1.749938287454663</v>
+        <v>1.623967327306092</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="O136">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="137">
@@ -8943,22 +8943,22 @@
         </is>
       </c>
       <c r="B137">
-        <v>0.6797221670917604</v>
+        <v>0.6105195804948748</v>
       </c>
       <c r="C137">
-        <v>0.241561793496524</v>
+        <v>0.2358520164007349</v>
       </c>
       <c r="D137">
-        <v>-1.598229324764594</v>
+        <v>-2.092180175490271</v>
       </c>
       <c r="E137">
-        <v>0.1099919496998897</v>
+        <v>0.03642240119795991</v>
       </c>
       <c r="F137">
-        <v>0.4233637427952222</v>
+        <v>0.3845404204363975</v>
       </c>
       <c r="G137">
-        <v>1.091312688671584</v>
+        <v>0.9692977340188028</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="O137">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="138">
@@ -9006,22 +9006,22 @@
         </is>
       </c>
       <c r="B138">
-        <v>0.7054016021966416</v>
+        <v>0.7113442351087553</v>
       </c>
       <c r="C138">
-        <v>0.1731342520119366</v>
+        <v>0.1628842187217447</v>
       </c>
       <c r="D138">
-        <v>-2.015707381968836</v>
+        <v>-2.091048554283016</v>
       </c>
       <c r="E138">
-        <v>0.04383058324857072</v>
+        <v>0.03652371170034316</v>
       </c>
       <c r="F138">
-        <v>0.5024169691190495</v>
+        <v>0.5169309293070036</v>
       </c>
       <c r="G138">
-        <v>0.9903953309022946</v>
+        <v>0.9788747241354213</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="O138">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="139">
@@ -9069,22 +9069,22 @@
         </is>
       </c>
       <c r="B139">
-        <v>0.9005388164444018</v>
+        <v>0.8800916685671285</v>
       </c>
       <c r="C139">
-        <v>0.2268992458231357</v>
+        <v>0.2179233782110026</v>
       </c>
       <c r="D139">
-        <v>-0.4617115825126828</v>
+        <v>-0.5861198057655164</v>
       </c>
       <c r="E139">
-        <v>0.6442881639132849</v>
+        <v>0.5577950075834898</v>
       </c>
       <c r="F139">
-        <v>0.5772520036122233</v>
+        <v>0.5741577005332247</v>
       </c>
       <c r="G139">
-        <v>1.404880632459206</v>
+        <v>1.349039374307671</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="O139">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="140">
@@ -9132,22 +9132,22 @@
         </is>
       </c>
       <c r="B140">
-        <v>0.8399855520907855</v>
+        <v>0.7721673236800872</v>
       </c>
       <c r="C140">
-        <v>0.1154183045024987</v>
+        <v>0.1339821863362419</v>
       </c>
       <c r="D140">
-        <v>-1.510770652334826</v>
+        <v>-1.92976409024315</v>
       </c>
       <c r="E140">
-        <v>0.1308468943713813</v>
+        <v>0.05363607477208667</v>
       </c>
       <c r="F140">
-        <v>0.6699271477797917</v>
+        <v>0.5938347056192866</v>
       </c>
       <c r="G140">
-        <v>1.053212621789717</v>
+        <v>1.004054444978037</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="O140">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="141">
@@ -9195,22 +9195,22 @@
         </is>
       </c>
       <c r="B141">
-        <v>1.042420635665977</v>
+        <v>1.05187781745497</v>
       </c>
       <c r="C141">
-        <v>0.09336275118888347</v>
+        <v>0.09621119399358154</v>
       </c>
       <c r="D141">
-        <v>0.444990560006561</v>
+        <v>0.5256869015690496</v>
       </c>
       <c r="E141">
-        <v>0.6563265761309607</v>
+        <v>0.5991057660861462</v>
       </c>
       <c r="F141">
-        <v>0.8681054488133244</v>
+        <v>0.8711043446107768</v>
       </c>
       <c r="G141">
-        <v>1.251738234275186</v>
+        <v>1.270165795520408</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="O141">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="142">
@@ -9258,22 +9258,22 @@
         </is>
       </c>
       <c r="B142">
-        <v>0.9795235367372473</v>
+        <v>0.894698027009752</v>
       </c>
       <c r="C142">
-        <v>0.1117175528112331</v>
+        <v>0.1280615905247704</v>
       </c>
       <c r="D142">
-        <v>-0.1851903485794108</v>
+        <v>-0.8688711203149236</v>
       </c>
       <c r="E142">
-        <v>0.8530797388803077</v>
+        <v>0.384917627296074</v>
       </c>
       <c r="F142">
-        <v>0.7869021332436865</v>
+        <v>0.6960977919377445</v>
       </c>
       <c r="G142">
-        <v>1.219295663956625</v>
+        <v>1.149959917710433</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="O142">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="143">
@@ -9321,22 +9321,22 @@
         </is>
       </c>
       <c r="B143">
-        <v>0.3501165222398964</v>
+        <v>0.2197380695487179</v>
       </c>
       <c r="C143">
-        <v>0.7377390595231894</v>
+        <v>0.8637275798969258</v>
       </c>
       <c r="D143">
-        <v>-1.422575158074662</v>
+        <v>-1.754394638052246</v>
       </c>
       <c r="E143">
-        <v>0.1548593496459907</v>
+        <v>0.07936290947256472</v>
       </c>
       <c r="F143">
-        <v>0.08246088280750262</v>
+        <v>0.04042956381798265</v>
       </c>
       <c r="G143">
-        <v>1.486542163652496</v>
+        <v>1.194294834007599</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         </is>
       </c>
       <c r="O143">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="144">
@@ -9384,22 +9384,22 @@
         </is>
       </c>
       <c r="B144">
-        <v>1.209123997809922</v>
+        <v>1.240124148153173</v>
       </c>
       <c r="C144">
-        <v>0.5834682619374904</v>
+        <v>0.5923182392595764</v>
       </c>
       <c r="D144">
-        <v>0.325460939441695</v>
+        <v>0.3633376111340319</v>
       </c>
       <c r="E144">
-        <v>0.7448322405826993</v>
+        <v>0.7163527006778974</v>
       </c>
       <c r="F144">
-        <v>0.3853201811920099</v>
+        <v>0.3884033481442758</v>
       </c>
       <c r="G144">
-        <v>3.794197432268217</v>
+        <v>3.95956396921008</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="O144">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="145">
@@ -9447,22 +9447,22 @@
         </is>
       </c>
       <c r="B145">
-        <v>0.7738133991358632</v>
+        <v>0.4825228768735469</v>
       </c>
       <c r="C145">
-        <v>0.7025510216963778</v>
+        <v>0.8088508532162655</v>
       </c>
       <c r="D145">
-        <v>-0.3649906027138307</v>
+        <v>-0.9009410612846334</v>
       </c>
       <c r="E145">
-        <v>0.7151184210222203</v>
+        <v>0.3676196577330573</v>
       </c>
       <c r="F145">
-        <v>0.1952646969404485</v>
+        <v>0.09886050258745648</v>
       </c>
       <c r="G145">
-        <v>3.066540885600103</v>
+        <v>2.355119796203278</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="O145">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="146">
@@ -9510,22 +9510,22 @@
         </is>
       </c>
       <c r="B146">
-        <v>0.3789596467081622</v>
+        <v>0.2351503288826194</v>
       </c>
       <c r="C146">
-        <v>0.6377901612018376</v>
+        <v>0.7546635474890941</v>
       </c>
       <c r="D146">
-        <v>-1.52138683168998</v>
+        <v>-1.918113411997281</v>
       </c>
       <c r="E146">
-        <v>0.1281627914606225</v>
+        <v>0.05509663220215912</v>
       </c>
       <c r="F146">
-        <v>0.1085687899349092</v>
+        <v>0.05357655863269874</v>
       </c>
       <c r="G146">
-        <v>1.322759643165173</v>
+        <v>1.032087140062335</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="O146">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="147">
@@ -9573,22 +9573,22 @@
         </is>
       </c>
       <c r="B147">
-        <v>1.203859194039121</v>
+        <v>1.291693519163865</v>
       </c>
       <c r="C147">
-        <v>0.5294947231767104</v>
+        <v>0.5456673382815994</v>
       </c>
       <c r="D147">
-        <v>0.350395166286131</v>
+        <v>0.4690663065105652</v>
       </c>
       <c r="E147">
-        <v>0.7260421534956014</v>
+        <v>0.6390222417793004</v>
       </c>
       <c r="F147">
-        <v>0.4264508342913027</v>
+        <v>0.4432886381939662</v>
       </c>
       <c r="G147">
-        <v>3.398462009063723</v>
+        <v>3.763850466024963</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="O147">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="148">
@@ -9636,22 +9636,22 @@
         </is>
       </c>
       <c r="B148">
-        <v>0.906860005697372</v>
+        <v>0.5370053015956342</v>
       </c>
       <c r="C148">
-        <v>0.6072287173809131</v>
+        <v>0.7096037311908799</v>
       </c>
       <c r="D148">
-        <v>-0.1610055432435096</v>
+        <v>-0.8761894626188077</v>
       </c>
       <c r="E148">
-        <v>0.872089034727104</v>
+        <v>0.3809270440345996</v>
       </c>
       <c r="F148">
-        <v>0.2758457059602432</v>
+        <v>0.1336480979152093</v>
       </c>
       <c r="G148">
-        <v>2.981358970481734</v>
+        <v>2.157716409288311</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         </is>
       </c>
       <c r="O148">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="149">
@@ -9699,22 +9699,22 @@
         </is>
       </c>
       <c r="B149">
-        <v>0.9176203929576412</v>
+        <v>0.9059024238547807</v>
       </c>
       <c r="C149">
-        <v>0.04804878730255667</v>
+        <v>0.046727304198953</v>
       </c>
       <c r="D149">
-        <v>-1.789254089557146</v>
+        <v>-2.114902204886081</v>
       </c>
       <c r="E149">
-        <v>0.07357390419996544</v>
+        <v>0.03443828323733512</v>
       </c>
       <c r="F149">
-        <v>0.8351487871567844</v>
+        <v>0.826622206825591</v>
       </c>
       <c r="G149">
-        <v>1.008236135309935</v>
+        <v>0.9927862991940133</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="O149">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="150">
@@ -9762,22 +9762,22 @@
         </is>
       </c>
       <c r="B150">
-        <v>1.012576217729958</v>
+        <v>1.033857557894931</v>
       </c>
       <c r="C150">
-        <v>0.05212259410134966</v>
+        <v>0.04809978528617898</v>
       </c>
       <c r="D150">
-        <v>0.2397768981227429</v>
+        <v>0.6922485844056179</v>
       </c>
       <c r="E150">
-        <v>0.8105032172224538</v>
+        <v>0.4887812326979422</v>
       </c>
       <c r="F150">
-        <v>0.9142414140158895</v>
+        <v>0.9408450308583699</v>
       </c>
       <c r="G150">
-        <v>1.121487805073866</v>
+        <v>1.136065361413778</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="O150">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="151">
@@ -9825,22 +9825,22 @@
         </is>
       </c>
       <c r="B151">
-        <v>0.9750954952847901</v>
+        <v>0.956601926766061</v>
       </c>
       <c r="C151">
-        <v>0.04279374733591456</v>
+        <v>0.04222623627078115</v>
       </c>
       <c r="D151">
-        <v>-0.5893353695033144</v>
+        <v>-1.050719587507493</v>
       </c>
       <c r="E151">
-        <v>0.5556363226803069</v>
+        <v>0.2933873971017037</v>
       </c>
       <c r="F151">
-        <v>0.8966460638470922</v>
+        <v>0.8806193292153891</v>
       </c>
       <c r="G151">
-        <v>1.060408630853963</v>
+        <v>1.039140541132411</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="O151">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="152">
@@ -9888,22 +9888,22 @@
         </is>
       </c>
       <c r="B152">
-        <v>0.4810290648408213</v>
+        <v>0.3842422121067757</v>
       </c>
       <c r="C152">
-        <v>0.5812157110069283</v>
+        <v>0.5912487541246387</v>
       </c>
       <c r="D152">
-        <v>-1.259132488985192</v>
+        <v>-1.617732228394624</v>
       </c>
       <c r="E152">
-        <v>0.2079824812434026</v>
+        <v>0.1057203173154191</v>
       </c>
       <c r="F152">
-        <v>0.1539712402457303</v>
+        <v>0.1205960885417234</v>
       </c>
       <c r="G152">
-        <v>1.502806373790001</v>
+        <v>1.224269205991931</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         </is>
       </c>
       <c r="O152">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="153">
@@ -9951,22 +9951,22 @@
         </is>
       </c>
       <c r="B153">
-        <v>1.297191726069912</v>
+        <v>1.507949119336869</v>
       </c>
       <c r="C153">
-        <v>0.5340788659489937</v>
+        <v>0.4957053818215057</v>
       </c>
       <c r="D153">
-        <v>0.4871971795192743</v>
+        <v>0.8286182550901824</v>
       </c>
       <c r="E153">
-        <v>0.6261186039210251</v>
+        <v>0.4073204548741716</v>
       </c>
       <c r="F153">
-        <v>0.4554025048524699</v>
+        <v>0.5707441936660197</v>
       </c>
       <c r="G153">
-        <v>3.694987085609815</v>
+        <v>3.984115075972993</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         </is>
       </c>
       <c r="O153">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="154">
@@ -10014,22 +10014,22 @@
         </is>
       </c>
       <c r="B154">
-        <v>0.8422997444385714</v>
+        <v>0.6456298110461606</v>
       </c>
       <c r="C154">
-        <v>0.5408426886515487</v>
+        <v>0.5480255622180049</v>
       </c>
       <c r="D154">
-        <v>-0.3173184008418172</v>
+        <v>-0.798373319667079</v>
       </c>
       <c r="E154">
-        <v>0.7510020164362955</v>
+        <v>0.4246538813595064</v>
       </c>
       <c r="F154">
-        <v>0.2918102466682456</v>
+        <v>0.2205481254446041</v>
       </c>
       <c r="G154">
-        <v>2.431267810440756</v>
+        <v>1.89000859595245</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         </is>
       </c>
       <c r="O154">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="155">
@@ -10077,22 +10077,22 @@
         </is>
       </c>
       <c r="B155">
-        <v>0.5485292311124665</v>
+        <v>0.475400090832191</v>
       </c>
       <c r="C155">
-        <v>0.3417535334795307</v>
+        <v>0.3415220955574819</v>
       </c>
       <c r="D155">
-        <v>-1.757157275746388</v>
+        <v>-2.177307245018756</v>
       </c>
       <c r="E155">
-        <v>0.07889100532258447</v>
+        <v>0.02945765098450991</v>
       </c>
       <c r="F155">
-        <v>0.2807363447331793</v>
+        <v>0.2434193652410956</v>
       </c>
       <c r="G155">
-        <v>1.07176830869834</v>
+        <v>0.9284604211312756</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="O155">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="156">
@@ -10140,22 +10140,22 @@
         </is>
       </c>
       <c r="B156">
-        <v>0.9844988217036317</v>
+        <v>1.150306335024613</v>
       </c>
       <c r="C156">
-        <v>0.3481020255061849</v>
+        <v>0.3259837668107826</v>
       </c>
       <c r="D156">
-        <v>-0.04487930723316091</v>
+        <v>0.4295560068986956</v>
       </c>
       <c r="E156">
-        <v>0.9642035106587062</v>
+        <v>0.6675186446715887</v>
       </c>
       <c r="F156">
-        <v>0.4976341996649324</v>
+        <v>0.6072054014274353</v>
       </c>
       <c r="G156">
-        <v>1.947691558555355</v>
+        <v>2.179171432413365</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="O156">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="157">
@@ -10203,22 +10203,22 @@
         </is>
       </c>
       <c r="B157">
-        <v>0.9025450908009091</v>
+        <v>0.7563957028491524</v>
       </c>
       <c r="C157">
-        <v>0.3012781906541359</v>
+        <v>0.3043206521175254</v>
       </c>
       <c r="D157">
-        <v>-0.3403387005686251</v>
+        <v>-0.9174225322120744</v>
       </c>
       <c r="E157">
-        <v>0.733601475917124</v>
+        <v>0.3589212699962488</v>
       </c>
       <c r="F157">
-        <v>0.500058078189591</v>
+        <v>0.4165919217806751</v>
       </c>
       <c r="G157">
-        <v>1.628986064734625</v>
+        <v>1.373369067847353</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         </is>
       </c>
       <c r="O157">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
   </sheetData>
